--- a/reports/Debug-snowbowl-20251230/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Week Ending (Actual)_Visits.xlsx
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C2" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,13 +445,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>585</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,13 +459,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C4" s="2">
-        <v>1717</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +473,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -487,10 +487,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -501,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C7" s="2">
-        <v>511</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -515,13 +515,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>1715</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C9" s="2">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>6</v>
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C11" s="2">
-        <v>603</v>
+        <v>511</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,7 +574,7 @@
         <v>46020</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>46020</v>
       </c>
       <c r="C13" s="2">
-        <v>1703</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>46021</v>
       </c>
       <c r="C14" s="2">
-        <v>451</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,7 +616,7 @@
         <v>46020</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>6</v>
@@ -630,10 +630,10 @@
         <v>46020</v>
       </c>
       <c r="C16" s="2">
-        <v>48</v>
+        <v>1703</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>46021</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>451</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
